--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120617511</v>
+        <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>93197</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rotmyren, Rotmyren, Upl</t>
+          <t>rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702931</v>
+        <v>703361</v>
       </c>
       <c r="R4" t="n">
-        <v>6659343</v>
+        <v>6659313</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,65 +979,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120617511</t>
+          <t>https://artportalen.se/Sighting/136976445</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120611443</v>
+        <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rotmyren, Rotmyren, Upl</t>
+          <t>rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703385</v>
+        <v>703376</v>
       </c>
       <c r="R5" t="n">
-        <v>6659523</v>
+        <v>6659301</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,65 +1091,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120611443</t>
+          <t>https://artportalen.se/Sighting/136976446</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120608702</v>
+        <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
+        <v>92338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rotmyren, Rotmyren, Upl</t>
+          <t>rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703444</v>
+        <v>702909</v>
       </c>
       <c r="R6" t="n">
-        <v>6659577</v>
+        <v>6659274</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1173,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1203,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120608702</t>
+          <t>https://artportalen.se/Sighting/136976461</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120608993</v>
+        <v>120617511</v>
       </c>
       <c r="B7" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>703480</v>
+        <v>702931</v>
       </c>
       <c r="R7" t="n">
-        <v>6659603</v>
+        <v>6659343</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,38 +1316,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120608993</t>
+          <t>https://artportalen.se/Sighting/120617511</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120617422</v>
+        <v>120611443</v>
       </c>
       <c r="B8" t="n">
-        <v>93235</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>702948</v>
+        <v>703385</v>
       </c>
       <c r="R8" t="n">
-        <v>6659336</v>
+        <v>6659523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,54 +1418,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120617422</t>
+          <t>https://artportalen.se/Sighting/120611443</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120609377</v>
+        <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>92076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rotmyren, Rotmyren, Upl</t>
+          <t>rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>703454</v>
+        <v>703282</v>
       </c>
       <c r="R9" t="n">
-        <v>6659624</v>
+        <v>6659588</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,65 +1519,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120609377</t>
+          <t>https://artportalen.se/Sighting/136976481</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120596867</v>
+        <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>5178</v>
+        <v>92076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102204</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långrudan, Långrudan, Upl</t>
+          <t>rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>702979</v>
+        <v>703403</v>
       </c>
       <c r="R10" t="n">
-        <v>6659114</v>
+        <v>6659553</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1601,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,71 +1631,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120596867</t>
+          <t>https://artportalen.se/Sighting/136976482</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120596538</v>
+        <v>120608702</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>702844</v>
+        <v>703444</v>
       </c>
       <c r="R11" t="n">
-        <v>6659257</v>
+        <v>6659577</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,60 +1744,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120596538</t>
+          <t>https://artportalen.se/Sighting/120608702</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120600055</v>
+        <v>120608993</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703056</v>
+        <v>703480</v>
       </c>
       <c r="R12" t="n">
-        <v>6659258</v>
+        <v>6659603</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,60 +1846,51 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120600055</t>
+          <t>https://artportalen.se/Sighting/120608993</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120611152</v>
+        <v>120617422</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703387</v>
+        <v>702948</v>
       </c>
       <c r="R13" t="n">
-        <v>6659553</v>
+        <v>6659336</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,60 +1948,51 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120611152</t>
+          <t>https://artportalen.se/Sighting/120617422</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120613848</v>
+        <v>120609377</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rotmyren, Rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703211</v>
+        <v>703454</v>
       </c>
       <c r="R14" t="n">
-        <v>6659581</v>
+        <v>6659624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,16 +2050,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120613848</t>
+          <t>https://artportalen.se/Sighting/120609377</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120596988</v>
+        <v>136976460</v>
       </c>
       <c r="B15" t="n">
-        <v>106244</v>
+        <v>58005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,37 +2067,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rotmyren, Rotmyren, Upl</t>
+          <t>rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703042</v>
+        <v>702915</v>
       </c>
       <c r="R15" t="n">
-        <v>6659192</v>
+        <v>6659279</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2107,12 +2126,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2127,27 +2156,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120596988</t>
+          <t>https://artportalen.se/Sighting/136976460</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120599053</v>
+        <v>136976439</v>
       </c>
       <c r="B16" t="n">
-        <v>106244</v>
+        <v>57195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2155,37 +2184,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rotmyren, Rotmyren, Upl</t>
+          <t>rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703040</v>
+        <v>703417</v>
       </c>
       <c r="R16" t="n">
-        <v>6659246</v>
+        <v>6659299</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2209,12 +2247,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,27 +2277,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120599053</t>
+          <t>https://artportalen.se/Sighting/136976439</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106521436</v>
+        <v>136976479</v>
       </c>
       <c r="B17" t="n">
-        <v>101326</v>
+        <v>57195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2257,37 +2305,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stormossen, Upl</t>
+          <t>rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702971</v>
+        <v>703249</v>
       </c>
       <c r="R17" t="n">
-        <v>6659192</v>
+        <v>6659601</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2311,12 +2359,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2331,31 +2394,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>David Falk</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>David Falk, David Falk</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Stora Obrutna Skogsområden</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106521436</t>
+          <t>https://artportalen.se/Sighting/136976479</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120596781</v>
+        <v>136976465</v>
       </c>
       <c r="B18" t="n">
-        <v>101326</v>
+        <v>5182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,37 +2422,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rotmyren, Rotmyren, Upl</t>
+          <t>rotmyren, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702970</v>
+        <v>702871</v>
       </c>
       <c r="R18" t="n">
-        <v>6659129</v>
+        <v>6659244</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2417,12 +2476,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2437,18 +2506,3427 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136976465</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136976468</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>702958</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6659118</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976468</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120596867</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långrudan, Långrudan, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>702979</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6659114</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596867</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136976442</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>703391</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6659321</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976442</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136976455</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>703023</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6659236</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976455</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136976457</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>703000</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6659241</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976457</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136976464</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>702872</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6659258</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976464</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136976466</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>702929</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6659115</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976466</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136976476</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>703296</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6659491</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976476</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136976478</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>703339</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6659528</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976478</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136976480</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>703270</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6659600</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976480</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136976452</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>703073</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6659246</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976452</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136976459</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>702928</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6659309</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976459</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136976448</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>703325</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6659307</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976448</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120596538</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>702844</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6659257</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596538</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120600055</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>703056</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6659258</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120600055</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120611152</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>703387</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6659553</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120611152</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120613848</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>703211</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6659581</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120613848</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136976451</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>703073</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6659246</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976451</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136976453</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>703051</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6659254</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976453</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120596988</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>703042</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6659192</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596988</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120599053</v>
+      </c>
+      <c r="B39" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>703040</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6659246</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120599053</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136976477</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106494</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>703327</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6659516</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976477</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136976473</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98209</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>702982</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6659160</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976473</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>106521436</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stormossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>702971</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6659192</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>David Falk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>David Falk, David Falk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521436</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120596781</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Rotmyren, Rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>702970</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6659129</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/120596781</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136976443</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>703371</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6659323</v>
+      </c>
+      <c r="S44" t="n">
+        <v>6</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976443</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136976467</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>702950</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6659136</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976467</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136976470</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>702980</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6659101</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976470</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136976472</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>702979</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6659152</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976472</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136976474</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>rotmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>702982</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6659165</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136976474</t>
         </is>
       </c>
     </row>
@@ -2471,6 +5949,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92338</v>
+        <v>92340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98209</v>
+        <v>98215</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92340</v>
+        <v>92342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98215</v>
+        <v>98217</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92342</v>
+        <v>92343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98217</v>
+        <v>98218</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92343</v>
+        <v>92349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92349</v>
+        <v>92353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98224</v>
+        <v>98228</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -4496,7 +4496,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92353</v>
+        <v>92355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98230</v>
+        <v>98232</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92355</v>
+        <v>92368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>136976460</v>
       </c>
       <c r="B15" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>136976439</v>
       </c>
       <c r="B16" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136976479</v>
       </c>
       <c r="B17" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>136976452</v>
       </c>
       <c r="B29" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136976459</v>
       </c>
       <c r="B30" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98232</v>
+        <v>98245</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92368</v>
+        <v>92370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>136976460</v>
       </c>
       <c r="B15" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>136976439</v>
       </c>
       <c r="B16" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136976479</v>
       </c>
       <c r="B17" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>136976452</v>
       </c>
       <c r="B29" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136976459</v>
       </c>
       <c r="B30" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>136976448</v>
       </c>
       <c r="B31" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -2085,11 +2085,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>rotmyren, Upl</t>
@@ -2206,11 +2202,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>rotmyren, Upl</t>
@@ -3732,11 +3724,7 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>rotmyren, Upl</t>
@@ -3849,11 +3837,7 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>rotmyren, Upl</t>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98247</v>
+        <v>98250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92373</v>
+        <v>92383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>136976460</v>
       </c>
       <c r="B15" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136976439</v>
       </c>
       <c r="B16" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>136976479</v>
       </c>
       <c r="B17" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>136976465</v>
       </c>
       <c r="B18" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>136976468</v>
       </c>
       <c r="B19" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136976442</v>
       </c>
       <c r="B21" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>136976455</v>
       </c>
       <c r="B22" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>136976457</v>
       </c>
       <c r="B23" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136976464</v>
       </c>
       <c r="B24" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>136976466</v>
       </c>
       <c r="B25" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136976476</v>
       </c>
       <c r="B26" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>136976478</v>
       </c>
       <c r="B27" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136976480</v>
       </c>
       <c r="B28" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136976452</v>
       </c>
       <c r="B29" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>136976459</v>
       </c>
       <c r="B30" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>136976448</v>
       </c>
       <c r="B31" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98250</v>
+        <v>98260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98260</v>
+        <v>98261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>136976460</v>
       </c>
       <c r="B15" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136976439</v>
       </c>
       <c r="B16" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>136976479</v>
       </c>
       <c r="B17" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136976452</v>
       </c>
       <c r="B29" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>136976459</v>
       </c>
       <c r="B30" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98261</v>
+        <v>98266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98266</v>
+        <v>98268</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>136976460</v>
       </c>
       <c r="B15" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136976452</v>
       </c>
       <c r="B29" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>136976459</v>
       </c>
       <c r="B30" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98268</v>
+        <v>98274</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98274</v>
+        <v>98286</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98286</v>
+        <v>98287</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98287</v>
+        <v>98290</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92410</v>
+        <v>92411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106588</v>
+        <v>106590</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47274-2024 artfynd.xlsx
+++ b/artfynd/A 47274-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136976445</v>
       </c>
       <c r="B4" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136976446</v>
       </c>
       <c r="B5" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136976461</v>
       </c>
       <c r="B6" t="n">
-        <v>92411</v>
+        <v>92414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136976481</v>
       </c>
       <c r="B9" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136976482</v>
       </c>
       <c r="B10" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>136976460</v>
       </c>
       <c r="B15" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136976439</v>
       </c>
       <c r="B16" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>136976479</v>
       </c>
       <c r="B17" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136976452</v>
       </c>
       <c r="B29" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>136976459</v>
       </c>
       <c r="B30" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>136976451</v>
       </c>
       <c r="B36" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>136976453</v>
       </c>
       <c r="B37" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136976477</v>
       </c>
       <c r="B40" t="n">
-        <v>106590</v>
+        <v>106594</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>136976473</v>
       </c>
       <c r="B41" t="n">
-        <v>98291</v>
+        <v>98294</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>136976443</v>
       </c>
       <c r="B44" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136976467</v>
       </c>
       <c r="B45" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136976470</v>
       </c>
       <c r="B46" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>136976472</v>
       </c>
       <c r="B47" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>136976474</v>
       </c>
       <c r="B48" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
